--- a/data-raw/delgadillolopez.sesame.uniformity.xlsx
+++ b/data-raw/delgadillolopez.sesame.uniformity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\drop\rpack\agridat\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1963C5AA-5033-49BA-B0E6-E8204E5F90F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5305E531-C634-4D79-AEC4-23835364C04E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44685" yWindow="0" windowWidth="12945" windowHeight="16305" xr2:uid="{FE13EB26-DF20-48F1-9328-0D797E03FBDB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{FE13EB26-DF20-48F1-9328-0D797E03FBDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1613,8 +1613,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Arial"&amp;10&amp;K000000 ---Internal Use--- </oddFooter>
-  </headerFooter>
 </worksheet>
 </file>